--- a/document/DB.xlsx
+++ b/document/DB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sekiguchi\Documents\HouseholdAccountBook\資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sekiguchi\Documents\HouseholdAccountBook\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71DA9D7-E3DD-4156-9A37-57D25300EE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA60DC8-823C-499F-A6F5-499AD9131F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -355,7 +355,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -921,10 +920,10 @@
       <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="3"/>
@@ -932,7 +931,7 @@
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -959,7 +958,7 @@
       <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="3" t="s">

--- a/document/DB.xlsx
+++ b/document/DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sekiguchi\Documents\HouseholdAccountBook\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA60DC8-823C-499F-A6F5-499AD9131F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58F8AB4-373C-45B8-A0F2-6B0E27995D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル一覧" sheetId="1" r:id="rId1"/>
@@ -884,7 +884,7 @@
         <v>31</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
